--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202646</v>
+        <v>120202732</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566438</v>
+        <v>566478</v>
       </c>
       <c r="R2" t="n">
-        <v>7040662</v>
+        <v>7040648</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120202105</v>
+        <v>120202606</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566450</v>
+        <v>566550</v>
       </c>
       <c r="R3" t="n">
-        <v>7040699</v>
+        <v>7040706</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120202660</v>
+        <v>120202551</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>91005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566446</v>
+        <v>566550</v>
       </c>
       <c r="R4" t="n">
-        <v>7040643</v>
+        <v>7040702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202044</v>
+        <v>120202105</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566460</v>
+        <v>566450</v>
       </c>
       <c r="R5" t="n">
-        <v>7040713</v>
+        <v>7040699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202606</v>
+        <v>120202483</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1148,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566550</v>
+        <v>566523</v>
       </c>
       <c r="R6" t="n">
-        <v>7040706</v>
+        <v>7040699</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202424</v>
+        <v>120202383</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566498</v>
+        <v>566446</v>
       </c>
       <c r="R7" t="n">
-        <v>7040708</v>
+        <v>7040659</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120202483</v>
+        <v>120202044</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,16 +1377,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1396,21 +1395,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566523</v>
+        <v>566460</v>
       </c>
       <c r="R8" t="n">
-        <v>7040699</v>
+        <v>7040713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1466,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1591,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203417</v>
+        <v>120202646</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,35 +1602,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1640,13 +1635,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566658</v>
+        <v>566438</v>
       </c>
       <c r="R10" t="n">
-        <v>7040621</v>
+        <v>7040662</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120202383</v>
+        <v>120202660</v>
       </c>
       <c r="B11" t="n">
         <v>90562</v>
@@ -1755,7 +1750,7 @@
         <v>566446</v>
       </c>
       <c r="R11" t="n">
-        <v>7040659</v>
+        <v>7040643</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,7 +1819,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120202732</v>
+        <v>120203417</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1859,12 +1854,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1873,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566478</v>
+        <v>566658</v>
       </c>
       <c r="R12" t="n">
-        <v>7040648</v>
+        <v>7040621</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120202551</v>
+        <v>120202424</v>
       </c>
       <c r="B13" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,25 +1952,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1985,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566550</v>
+        <v>566498</v>
       </c>
       <c r="R13" t="n">
-        <v>7040702</v>
+        <v>7040708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2025,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,6 +2054,906 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120221156</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>566460</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7040637</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120221395</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>566519</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7040662</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120202614</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90916</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>566449</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7040675</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120219545</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dalsberget, Dalsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>566469</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7040750</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120219595</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>566472</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7040700</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120221446</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>566514</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7040671</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120219588</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>566478</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7040703</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120221265</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>566490</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7040653</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120202660</v>
+        <v>120203417</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,38 +1719,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566446</v>
+        <v>566658</v>
       </c>
       <c r="R11" t="n">
-        <v>7040643</v>
+        <v>7040621</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120203417</v>
+        <v>120202660</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,47 +1840,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566658</v>
+        <v>566446</v>
       </c>
       <c r="R12" t="n">
-        <v>7040621</v>
+        <v>7040643</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2509,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120219595</v>
+        <v>120221446</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,25 +2521,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566472</v>
+        <v>566514</v>
       </c>
       <c r="R18" t="n">
-        <v>7040700</v>
+        <v>7040671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,22 +2609,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120221446</v>
+        <v>120219595</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,25 +2633,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566514</v>
+        <v>566472</v>
       </c>
       <c r="R19" t="n">
-        <v>7040671</v>
+        <v>7040700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,12 +2721,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120202614</v>
+        <v>120219545</v>
       </c>
       <c r="B16" t="n">
-        <v>90916</v>
+        <v>90527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,38 +2297,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1506</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566449</v>
+        <v>566469</v>
       </c>
       <c r="R16" t="n">
-        <v>7040675</v>
+        <v>7040750</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,22 +2355,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,22 +2385,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120219545</v>
+        <v>120221446</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,38 +2409,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566469</v>
+        <v>566514</v>
       </c>
       <c r="R17" t="n">
-        <v>7040750</v>
+        <v>7040671</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120221446</v>
+        <v>120219595</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,25 +2521,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566514</v>
+        <v>566472</v>
       </c>
       <c r="R18" t="n">
-        <v>7040671</v>
+        <v>7040700</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,22 +2609,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120219595</v>
+        <v>120219588</v>
       </c>
       <c r="B19" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,25 +2633,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566472</v>
+        <v>566478</v>
       </c>
       <c r="R19" t="n">
-        <v>7040700</v>
+        <v>7040703</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,19 +2721,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120219588</v>
+        <v>120221265</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566478</v>
+        <v>566490</v>
       </c>
       <c r="R20" t="n">
-        <v>7040703</v>
+        <v>7040653</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120221265</v>
+        <v>120202704</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566490</v>
+        <v>566463</v>
       </c>
       <c r="R21" t="n">
-        <v>7040653</v>
+        <v>7040636</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,22 +2915,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,12 +2945,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2397,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120221446</v>
+        <v>120219595</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,25 +2409,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566514</v>
+        <v>566472</v>
       </c>
       <c r="R17" t="n">
-        <v>7040671</v>
+        <v>7040700</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,22 +2497,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120219595</v>
+        <v>120221446</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,25 +2521,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566472</v>
+        <v>566514</v>
       </c>
       <c r="R18" t="n">
-        <v>7040700</v>
+        <v>7040671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,12 +2609,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202732</v>
+        <v>120202696</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>100167</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566478</v>
+        <v>566575</v>
       </c>
       <c r="R2" t="n">
-        <v>7040648</v>
+        <v>7040696</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120202606</v>
+        <v>120203417</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566550</v>
+        <v>566658</v>
       </c>
       <c r="R3" t="n">
-        <v>7040706</v>
+        <v>7040621</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120202551</v>
+        <v>120202646</v>
       </c>
       <c r="B4" t="n">
-        <v>91005</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,41 +920,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566550</v>
+        <v>566438</v>
       </c>
       <c r="R4" t="n">
-        <v>7040702</v>
+        <v>7040662</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202105</v>
+        <v>120202732</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1037,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566450</v>
+        <v>566478</v>
       </c>
       <c r="R5" t="n">
-        <v>7040699</v>
+        <v>7040648</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202483</v>
+        <v>120202551</v>
       </c>
       <c r="B6" t="n">
-        <v>57326</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,43 +1158,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566523</v>
+        <v>566550</v>
       </c>
       <c r="R6" t="n">
-        <v>7040699</v>
+        <v>7040702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202383</v>
+        <v>120202044</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,34 +1274,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566446</v>
+        <v>566460</v>
       </c>
       <c r="R7" t="n">
-        <v>7040659</v>
+        <v>7040713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1343,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120202044</v>
+        <v>120202660</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,34 +1391,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566460</v>
+        <v>566446</v>
       </c>
       <c r="R8" t="n">
-        <v>7040713</v>
+        <v>7040643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120202696</v>
+        <v>120202606</v>
       </c>
       <c r="B9" t="n">
-        <v>100144</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1499,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566575</v>
+        <v>566550</v>
       </c>
       <c r="R9" t="n">
-        <v>7040696</v>
+        <v>7040706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120202646</v>
+        <v>120202105</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,42 +1615,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566438</v>
+        <v>566450</v>
       </c>
       <c r="R10" t="n">
-        <v>7040662</v>
+        <v>7040699</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203417</v>
+        <v>120202424</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,47 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566658</v>
+        <v>566498</v>
       </c>
       <c r="R11" t="n">
-        <v>7040621</v>
+        <v>7040708</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1796,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,22 +1816,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120202660</v>
+        <v>120202383</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>566446</v>
       </c>
       <c r="R12" t="n">
-        <v>7040643</v>
+        <v>7040659</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120202424</v>
+        <v>120202483</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1974,16 +1974,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566498</v>
+        <v>566523</v>
       </c>
       <c r="R13" t="n">
-        <v>7040708</v>
+        <v>7040699</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,12 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120221156</v>
+        <v>120221265</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,42 +2069,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566460</v>
+        <v>566490</v>
       </c>
       <c r="R14" t="n">
-        <v>7040637</v>
+        <v>7040653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120221395</v>
+        <v>120219588</v>
       </c>
       <c r="B15" t="n">
-        <v>5169</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,25 +2181,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2213,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566519</v>
+        <v>566478</v>
       </c>
       <c r="R15" t="n">
-        <v>7040662</v>
+        <v>7040703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2258,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,7 +2284,7 @@
         <v>120219545</v>
       </c>
       <c r="B16" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2397,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120219595</v>
+        <v>120221395</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>5169</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,21 +2409,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2437,10 +2433,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566472</v>
+        <v>566519</v>
       </c>
       <c r="R17" t="n">
-        <v>7040700</v>
+        <v>7040662</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,22 +2493,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120221446</v>
+        <v>120221156</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,38 +2517,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566514</v>
+        <v>566460</v>
       </c>
       <c r="R18" t="n">
-        <v>7040671</v>
+        <v>7040637</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120219588</v>
+        <v>120221446</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,21 +2637,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566478</v>
+        <v>566514</v>
       </c>
       <c r="R19" t="n">
-        <v>7040703</v>
+        <v>7040671</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120221265</v>
+        <v>120219595</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,25 +2745,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566490</v>
+        <v>566472</v>
       </c>
       <c r="R20" t="n">
-        <v>7040653</v>
+        <v>7040700</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,12 +2833,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2281,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120219545</v>
+        <v>120221395</v>
       </c>
       <c r="B16" t="n">
-        <v>90545</v>
+        <v>5169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,34 +2297,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566469</v>
+        <v>566519</v>
       </c>
       <c r="R16" t="n">
-        <v>7040750</v>
+        <v>7040662</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120221395</v>
+        <v>120219545</v>
       </c>
       <c r="B17" t="n">
-        <v>5169</v>
+        <v>90545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,34 +2409,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566519</v>
+        <v>566469</v>
       </c>
       <c r="R17" t="n">
-        <v>7040662</v>
+        <v>7040750</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202696</v>
+        <v>120202483</v>
       </c>
       <c r="B2" t="n">
-        <v>100167</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1365</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566575</v>
+        <v>566523</v>
       </c>
       <c r="R2" t="n">
-        <v>7040696</v>
+        <v>7040699</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120203417</v>
+        <v>120202660</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566658</v>
+        <v>566446</v>
       </c>
       <c r="R3" t="n">
-        <v>7040621</v>
+        <v>7040643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120202646</v>
+        <v>120202383</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,42 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566438</v>
+        <v>566446</v>
       </c>
       <c r="R4" t="n">
-        <v>7040662</v>
+        <v>7040659</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202732</v>
+        <v>120202105</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,47 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566478</v>
+        <v>566450</v>
       </c>
       <c r="R5" t="n">
-        <v>7040648</v>
+        <v>7040699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202551</v>
+        <v>120202424</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566550</v>
+        <v>566498</v>
       </c>
       <c r="R6" t="n">
-        <v>7040702</v>
+        <v>7040708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202044</v>
+        <v>120202551</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,38 +1257,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566460</v>
+        <v>566550</v>
       </c>
       <c r="R7" t="n">
-        <v>7040713</v>
+        <v>7040702</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120202660</v>
+        <v>120203417</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,38 +1369,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566446</v>
+        <v>566658</v>
       </c>
       <c r="R8" t="n">
-        <v>7040643</v>
+        <v>7040621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120202606</v>
+        <v>120202732</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,38 +1490,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566550</v>
+        <v>566478</v>
       </c>
       <c r="R9" t="n">
-        <v>7040706</v>
+        <v>7040648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120202105</v>
+        <v>120202044</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,34 +1615,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566450</v>
+        <v>566460</v>
       </c>
       <c r="R10" t="n">
-        <v>7040699</v>
+        <v>7040713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1684,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120202424</v>
+        <v>120202606</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,21 +1732,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566498</v>
+        <v>566550</v>
       </c>
       <c r="R11" t="n">
-        <v>7040708</v>
+        <v>7040706</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,12 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120202383</v>
+        <v>120202646</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,37 +1844,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566446</v>
+        <v>566438</v>
       </c>
       <c r="R12" t="n">
-        <v>7040659</v>
+        <v>7040662</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1918,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1945,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120202483</v>
+        <v>120202696</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>100167</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,43 +1957,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566523</v>
+        <v>566575</v>
       </c>
       <c r="R13" t="n">
-        <v>7040699</v>
+        <v>7040696</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2169,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120219588</v>
+        <v>120221395</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>5169</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566478</v>
+        <v>566519</v>
       </c>
       <c r="R15" t="n">
-        <v>7040703</v>
+        <v>7040662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120221395</v>
+        <v>120219545</v>
       </c>
       <c r="B16" t="n">
-        <v>5169</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,34 +2297,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566519</v>
+        <v>566469</v>
       </c>
       <c r="R16" t="n">
-        <v>7040662</v>
+        <v>7040750</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120219545</v>
+        <v>120221156</v>
       </c>
       <c r="B17" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,38 +2405,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566469</v>
+        <v>566460</v>
       </c>
       <c r="R17" t="n">
-        <v>7040750</v>
+        <v>7040637</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2482,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120221156</v>
+        <v>120219588</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,42 +2521,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566460</v>
+        <v>566478</v>
       </c>
       <c r="R18" t="n">
-        <v>7040637</v>
+        <v>7040703</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202483</v>
+        <v>120202660</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566523</v>
+        <v>566446</v>
       </c>
       <c r="R2" t="n">
-        <v>7040699</v>
+        <v>7040643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120202660</v>
+        <v>120202646</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566446</v>
+        <v>566438</v>
       </c>
       <c r="R3" t="n">
-        <v>7040643</v>
+        <v>7040662</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120202383</v>
+        <v>120203417</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +916,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566446</v>
+        <v>566658</v>
       </c>
       <c r="R4" t="n">
-        <v>7040659</v>
+        <v>7040621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202105</v>
+        <v>120202483</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,31 +1041,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566450</v>
+        <v>566523</v>
       </c>
       <c r="R5" t="n">
         <v>7040699</v>
@@ -1091,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202424</v>
+        <v>120202732</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1154,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566498</v>
+        <v>566478</v>
       </c>
       <c r="R6" t="n">
-        <v>7040708</v>
+        <v>7040648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1251,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202551</v>
+        <v>120202105</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1275,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566550</v>
+        <v>566450</v>
       </c>
       <c r="R7" t="n">
-        <v>7040702</v>
+        <v>7040699</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120203417</v>
+        <v>120202383</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,47 +1387,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566658</v>
+        <v>566446</v>
       </c>
       <c r="R8" t="n">
-        <v>7040621</v>
+        <v>7040659</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120202732</v>
+        <v>120202044</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,47 +1499,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566478</v>
+        <v>566460</v>
       </c>
       <c r="R9" t="n">
-        <v>7040648</v>
+        <v>7040713</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120202044</v>
+        <v>120202696</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>100167</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,38 +1616,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566460</v>
+        <v>566575</v>
       </c>
       <c r="R10" t="n">
-        <v>7040713</v>
+        <v>7040696</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,12 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,22 +1704,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120202606</v>
+        <v>120202551</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,25 +1728,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,7 +1759,7 @@
         <v>566550</v>
       </c>
       <c r="R11" t="n">
-        <v>7040706</v>
+        <v>7040702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120202646</v>
+        <v>120202606</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,42 +1844,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566438</v>
+        <v>566550</v>
       </c>
       <c r="R12" t="n">
-        <v>7040662</v>
+        <v>7040706</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,22 +1928,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120202696</v>
+        <v>120202424</v>
       </c>
       <c r="B13" t="n">
-        <v>100167</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,25 +1952,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1985,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566575</v>
+        <v>566498</v>
       </c>
       <c r="R13" t="n">
-        <v>7040696</v>
+        <v>7040708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2025,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120221265</v>
+        <v>120219595</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,25 +2069,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566490</v>
+        <v>566472</v>
       </c>
       <c r="R14" t="n">
-        <v>7040653</v>
+        <v>7040700</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,22 +2157,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120221395</v>
+        <v>120219588</v>
       </c>
       <c r="B15" t="n">
-        <v>5169</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566519</v>
+        <v>566478</v>
       </c>
       <c r="R15" t="n">
-        <v>7040662</v>
+        <v>7040703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120221156</v>
+        <v>120221446</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,42 +2405,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566460</v>
+        <v>566514</v>
       </c>
       <c r="R17" t="n">
-        <v>7040637</v>
+        <v>7040671</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120219588</v>
+        <v>120221156</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,38 +2517,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566478</v>
+        <v>566460</v>
       </c>
       <c r="R18" t="n">
-        <v>7040703</v>
+        <v>7040637</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120221446</v>
+        <v>120221395</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,25 +2633,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566514</v>
+        <v>566519</v>
       </c>
       <c r="R19" t="n">
-        <v>7040671</v>
+        <v>7040662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120219595</v>
+        <v>120221265</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,25 +2745,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566472</v>
+        <v>566490</v>
       </c>
       <c r="R20" t="n">
-        <v>7040700</v>
+        <v>7040653</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,12 +2833,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202660</v>
+        <v>120202646</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566446</v>
+        <v>566438</v>
       </c>
       <c r="R2" t="n">
-        <v>7040643</v>
+        <v>7040662</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120202646</v>
+        <v>120202696</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>100167</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566438</v>
+        <v>566575</v>
       </c>
       <c r="R3" t="n">
-        <v>7040662</v>
+        <v>7040696</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202483</v>
+        <v>120202551</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,43 +1037,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566523</v>
+        <v>566550</v>
       </c>
       <c r="R5" t="n">
-        <v>7040699</v>
+        <v>7040702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202732</v>
+        <v>120202383</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,47 +1149,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566478</v>
+        <v>566446</v>
       </c>
       <c r="R6" t="n">
-        <v>7040648</v>
+        <v>7040659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202105</v>
+        <v>120202483</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,31 +1265,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566450</v>
+        <v>566523</v>
       </c>
       <c r="R7" t="n">
         <v>7040699</v>
@@ -1338,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,22 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120202383</v>
+        <v>120202105</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566446</v>
+        <v>566450</v>
       </c>
       <c r="R8" t="n">
-        <v>7040659</v>
+        <v>7040699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120202044</v>
+        <v>120202732</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,38 +1490,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566460</v>
+        <v>566478</v>
       </c>
       <c r="R9" t="n">
-        <v>7040713</v>
+        <v>7040648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,12 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120202696</v>
+        <v>120202606</v>
       </c>
       <c r="B10" t="n">
-        <v>100167</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,25 +1611,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566575</v>
+        <v>566550</v>
       </c>
       <c r="R10" t="n">
-        <v>7040696</v>
+        <v>7040706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120202551</v>
+        <v>120202424</v>
       </c>
       <c r="B11" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,25 +1723,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1756,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566550</v>
+        <v>566498</v>
       </c>
       <c r="R11" t="n">
-        <v>7040702</v>
+        <v>7040708</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1796,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120202606</v>
+        <v>120202044</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,34 +1844,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566550</v>
+        <v>566460</v>
       </c>
       <c r="R12" t="n">
-        <v>7040706</v>
+        <v>7040713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,22 +1933,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120202424</v>
+        <v>120202660</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1961,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1980,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566498</v>
+        <v>566446</v>
       </c>
       <c r="R13" t="n">
-        <v>7040708</v>
+        <v>7040643</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,12 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,22 +2045,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120219595</v>
+        <v>120221395</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>5169</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566472</v>
+        <v>566519</v>
       </c>
       <c r="R14" t="n">
-        <v>7040700</v>
+        <v>7040662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,22 +2157,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120219588</v>
+        <v>120221446</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566478</v>
+        <v>566514</v>
       </c>
       <c r="R15" t="n">
-        <v>7040703</v>
+        <v>7040671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120219545</v>
+        <v>120221265</v>
       </c>
       <c r="B16" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,38 +2293,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566469</v>
+        <v>566490</v>
       </c>
       <c r="R16" t="n">
-        <v>7040750</v>
+        <v>7040653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120221446</v>
+        <v>120221156</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,38 +2405,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566514</v>
+        <v>566460</v>
       </c>
       <c r="R17" t="n">
-        <v>7040671</v>
+        <v>7040637</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2482,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120221156</v>
+        <v>120219588</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,42 +2521,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566460</v>
+        <v>566478</v>
       </c>
       <c r="R18" t="n">
-        <v>7040637</v>
+        <v>7040703</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120221395</v>
+        <v>120219545</v>
       </c>
       <c r="B19" t="n">
-        <v>5169</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,34 +2637,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566519</v>
+        <v>566469</v>
       </c>
       <c r="R19" t="n">
-        <v>7040662</v>
+        <v>7040750</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120221265</v>
+        <v>120219595</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,25 +2745,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566490</v>
+        <v>566472</v>
       </c>
       <c r="R20" t="n">
-        <v>7040653</v>
+        <v>7040700</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,12 +2833,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202646</v>
+        <v>120202383</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566438</v>
+        <v>566446</v>
       </c>
       <c r="R2" t="n">
-        <v>7040662</v>
+        <v>7040659</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120202696</v>
+        <v>120203417</v>
       </c>
       <c r="B3" t="n">
-        <v>100167</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1365</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566575</v>
+        <v>566658</v>
       </c>
       <c r="R3" t="n">
-        <v>7040696</v>
+        <v>7040621</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120203417</v>
+        <v>120202606</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,47 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566658</v>
+        <v>566550</v>
       </c>
       <c r="R4" t="n">
-        <v>7040621</v>
+        <v>7040706</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202551</v>
+        <v>120202696</v>
       </c>
       <c r="B5" t="n">
-        <v>91023</v>
+        <v>100167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566550</v>
+        <v>566575</v>
       </c>
       <c r="R5" t="n">
-        <v>7040702</v>
+        <v>7040696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202383</v>
+        <v>120202551</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,25 +1144,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566446</v>
+        <v>566550</v>
       </c>
       <c r="R6" t="n">
-        <v>7040659</v>
+        <v>7040702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202483</v>
+        <v>120202105</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,36 +1260,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566523</v>
+        <v>566450</v>
       </c>
       <c r="R7" t="n">
         <v>7040699</v>
@@ -1329,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,22 +1344,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120202105</v>
+        <v>120202732</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,38 +1368,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566450</v>
+        <v>566478</v>
       </c>
       <c r="R8" t="n">
-        <v>7040699</v>
+        <v>7040648</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120202732</v>
+        <v>120202483</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,35 +1489,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1527,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566478</v>
+        <v>566523</v>
       </c>
       <c r="R9" t="n">
-        <v>7040648</v>
+        <v>7040699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1582,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120202606</v>
+        <v>120202424</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,21 +1610,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1639,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566550</v>
+        <v>566498</v>
       </c>
       <c r="R10" t="n">
-        <v>7040706</v>
+        <v>7040708</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1679,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120202424</v>
+        <v>120202646</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,37 +1727,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566498</v>
+        <v>566438</v>
       </c>
       <c r="R11" t="n">
-        <v>7040708</v>
+        <v>7040662</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,12 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,22 +1816,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120202044</v>
+        <v>120202660</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,34 +1844,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566460</v>
+        <v>566446</v>
       </c>
       <c r="R12" t="n">
-        <v>7040713</v>
+        <v>7040643</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,12 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120202660</v>
+        <v>120202044</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1961,34 +1956,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566446</v>
+        <v>566460</v>
       </c>
       <c r="R13" t="n">
-        <v>7040643</v>
+        <v>7040713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2025,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120221395</v>
+        <v>120221446</v>
       </c>
       <c r="B14" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,25 +2069,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566519</v>
+        <v>566514</v>
       </c>
       <c r="R14" t="n">
-        <v>7040662</v>
+        <v>7040671</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120221446</v>
+        <v>120219545</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,38 +2181,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566514</v>
+        <v>566469</v>
       </c>
       <c r="R15" t="n">
-        <v>7040671</v>
+        <v>7040750</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120221265</v>
+        <v>120219595</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,25 +2293,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566490</v>
+        <v>566472</v>
       </c>
       <c r="R16" t="n">
-        <v>7040653</v>
+        <v>7040700</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,22 +2381,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120221156</v>
+        <v>120219588</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,42 +2405,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566460</v>
+        <v>566478</v>
       </c>
       <c r="R17" t="n">
-        <v>7040637</v>
+        <v>7040703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120219588</v>
+        <v>120221156</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,38 +2517,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566478</v>
+        <v>566460</v>
       </c>
       <c r="R18" t="n">
-        <v>7040703</v>
+        <v>7040637</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120219545</v>
+        <v>120221395</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>5169</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,34 +2637,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566469</v>
+        <v>566519</v>
       </c>
       <c r="R19" t="n">
-        <v>7040750</v>
+        <v>7040662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120219595</v>
+        <v>120221265</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,25 +2745,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566472</v>
+        <v>566490</v>
       </c>
       <c r="R20" t="n">
-        <v>7040700</v>
+        <v>7040653</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,12 +2833,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202383</v>
+        <v>120202732</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566446</v>
+        <v>566478</v>
       </c>
       <c r="R2" t="n">
-        <v>7040659</v>
+        <v>7040648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120203417</v>
+        <v>120202551</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,43 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566658</v>
+        <v>566550</v>
       </c>
       <c r="R3" t="n">
-        <v>7040621</v>
+        <v>7040702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,19 +896,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120202606</v>
+        <v>120202383</v>
       </c>
       <c r="B4" t="n">
         <v>90580</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566550</v>
+        <v>566446</v>
       </c>
       <c r="R4" t="n">
-        <v>7040706</v>
+        <v>7040659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202696</v>
+        <v>120202105</v>
       </c>
       <c r="B5" t="n">
-        <v>100167</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566575</v>
+        <v>566450</v>
       </c>
       <c r="R5" t="n">
-        <v>7040696</v>
+        <v>7040699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202551</v>
+        <v>120202483</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,38 +1144,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566550</v>
+        <v>566523</v>
       </c>
       <c r="R6" t="n">
-        <v>7040702</v>
+        <v>7040699</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202105</v>
+        <v>120202660</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566450</v>
+        <v>566446</v>
       </c>
       <c r="R7" t="n">
-        <v>7040699</v>
+        <v>7040643</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120202732</v>
+        <v>120202424</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,47 +1373,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566478</v>
+        <v>566498</v>
       </c>
       <c r="R8" t="n">
-        <v>7040648</v>
+        <v>7040708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120202483</v>
+        <v>120203417</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,31 +1490,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1522,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566523</v>
+        <v>566658</v>
       </c>
       <c r="R9" t="n">
-        <v>7040699</v>
+        <v>7040621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120202424</v>
+        <v>120202606</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1615,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566498</v>
+        <v>566550</v>
       </c>
       <c r="R10" t="n">
-        <v>7040708</v>
+        <v>7040706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,12 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1828,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120202660</v>
+        <v>120202696</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>100167</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,25 +1840,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566446</v>
+        <v>566575</v>
       </c>
       <c r="R12" t="n">
-        <v>7040643</v>
+        <v>7040696</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,12 +1928,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120221446</v>
+        <v>120219595</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,25 +2069,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566514</v>
+        <v>566472</v>
       </c>
       <c r="R14" t="n">
-        <v>7040671</v>
+        <v>7040700</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,22 +2157,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120219545</v>
+        <v>120221265</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,38 +2181,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566469</v>
+        <v>566490</v>
       </c>
       <c r="R15" t="n">
-        <v>7040750</v>
+        <v>7040653</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120219595</v>
+        <v>120219588</v>
       </c>
       <c r="B16" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,25 +2293,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566472</v>
+        <v>566478</v>
       </c>
       <c r="R16" t="n">
-        <v>7040700</v>
+        <v>7040703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,22 +2381,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120219588</v>
+        <v>120221156</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,38 +2405,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566478</v>
+        <v>566460</v>
       </c>
       <c r="R17" t="n">
-        <v>7040703</v>
+        <v>7040637</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2482,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120221156</v>
+        <v>120221395</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,42 +2521,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566460</v>
+        <v>566519</v>
       </c>
       <c r="R18" t="n">
-        <v>7040637</v>
+        <v>7040662</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120221395</v>
+        <v>120221446</v>
       </c>
       <c r="B19" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,25 +2633,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566519</v>
+        <v>566514</v>
       </c>
       <c r="R19" t="n">
-        <v>7040662</v>
+        <v>7040671</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120221265</v>
+        <v>120219545</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,38 +2745,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566490</v>
+        <v>566469</v>
       </c>
       <c r="R20" t="n">
-        <v>7040653</v>
+        <v>7040750</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202732</v>
+        <v>120202606</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566478</v>
+        <v>566550</v>
       </c>
       <c r="R2" t="n">
-        <v>7040648</v>
+        <v>7040706</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120202551</v>
+        <v>120202424</v>
       </c>
       <c r="B3" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566550</v>
+        <v>566498</v>
       </c>
       <c r="R3" t="n">
-        <v>7040702</v>
+        <v>7040708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120202383</v>
+        <v>120203417</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +916,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566446</v>
+        <v>566658</v>
       </c>
       <c r="R4" t="n">
-        <v>7040659</v>
+        <v>7040621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202105</v>
+        <v>120202646</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,37 +1041,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566450</v>
+        <v>566438</v>
       </c>
       <c r="R5" t="n">
-        <v>7040699</v>
+        <v>7040662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202483</v>
+        <v>120202660</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,39 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566523</v>
+        <v>566446</v>
       </c>
       <c r="R6" t="n">
-        <v>7040699</v>
+        <v>7040643</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202660</v>
+        <v>120202732</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,38 +1266,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566446</v>
+        <v>566478</v>
       </c>
       <c r="R7" t="n">
-        <v>7040643</v>
+        <v>7040648</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120202424</v>
+        <v>120202483</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,16 +1391,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1395,16 +1409,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566498</v>
+        <v>566523</v>
       </c>
       <c r="R8" t="n">
-        <v>7040708</v>
+        <v>7040699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120203417</v>
+        <v>120202383</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,47 +1504,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566658</v>
+        <v>566446</v>
       </c>
       <c r="R9" t="n">
-        <v>7040621</v>
+        <v>7040659</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120202606</v>
+        <v>120202696</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>100167</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,25 +1616,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1639,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566550</v>
+        <v>566575</v>
       </c>
       <c r="R10" t="n">
-        <v>7040706</v>
+        <v>7040696</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120202646</v>
+        <v>120202551</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,46 +1728,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566438</v>
+        <v>566550</v>
       </c>
       <c r="R11" t="n">
-        <v>7040662</v>
+        <v>7040702</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,22 +1816,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120202696</v>
+        <v>120202044</v>
       </c>
       <c r="B12" t="n">
-        <v>100167</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,38 +1840,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566575</v>
+        <v>566460</v>
       </c>
       <c r="R12" t="n">
-        <v>7040696</v>
+        <v>7040713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,22 +1933,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120202044</v>
+        <v>120202105</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,34 +1961,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566460</v>
+        <v>566450</v>
       </c>
       <c r="R13" t="n">
-        <v>7040713</v>
+        <v>7040699</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,12 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120219595</v>
+        <v>120221265</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,25 +2069,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566472</v>
+        <v>566490</v>
       </c>
       <c r="R14" t="n">
-        <v>7040700</v>
+        <v>7040653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,22 +2157,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120221265</v>
+        <v>120219545</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,38 +2181,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566490</v>
+        <v>566469</v>
       </c>
       <c r="R15" t="n">
-        <v>7040653</v>
+        <v>7040750</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120219588</v>
+        <v>120221395</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>5169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,25 +2293,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566478</v>
+        <v>566519</v>
       </c>
       <c r="R16" t="n">
-        <v>7040703</v>
+        <v>7040662</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120221156</v>
+        <v>120219588</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,42 +2405,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566460</v>
+        <v>566478</v>
       </c>
       <c r="R17" t="n">
-        <v>7040637</v>
+        <v>7040703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120221395</v>
+        <v>120221446</v>
       </c>
       <c r="B18" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,25 +2517,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2549,10 +2545,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566519</v>
+        <v>566514</v>
       </c>
       <c r="R18" t="n">
-        <v>7040662</v>
+        <v>7040671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2580,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2590,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,10 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120221446</v>
+        <v>120219595</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,25 +2629,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566514</v>
+        <v>566472</v>
       </c>
       <c r="R19" t="n">
-        <v>7040671</v>
+        <v>7040700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,22 +2717,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120219545</v>
+        <v>120221156</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,38 +2741,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566469</v>
+        <v>566460</v>
       </c>
       <c r="R20" t="n">
-        <v>7040750</v>
+        <v>7040637</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202660</v>
+        <v>120202732</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,38 +1154,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566446</v>
+        <v>566478</v>
       </c>
       <c r="R6" t="n">
-        <v>7040643</v>
+        <v>7040648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202732</v>
+        <v>120202660</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,47 +1275,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566478</v>
+        <v>566446</v>
       </c>
       <c r="R7" t="n">
-        <v>7040648</v>
+        <v>7040643</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2955,6 +2955,117 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122246564</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100388</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>566575</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7040695</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Y-Sol-0322</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100388</v>
+        <v>100396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100396</v>
+        <v>100398</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100414</v>
+        <v>100424</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,11 +2960,11 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100424</v>
+        <v>100436</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100436</v>
+        <v>100441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,11 +2974,6 @@
       </c>
       <c r="E22" t="n">
         <v>1365</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100450</v>
+        <v>100463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,6 +2974,11 @@
       </c>
       <c r="E22" t="n">
         <v>1365</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100463</v>
+        <v>100476</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100476</v>
+        <v>100479</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100479</v>
+        <v>100480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100480</v>
+        <v>100483</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 41963-2024 artfynd.xlsx
+++ b/artfynd/A 41963-2024 artfynd.xlsx
@@ -2960,7 +2960,7 @@
         <v>122246564</v>
       </c>
       <c r="B22" t="n">
-        <v>100586</v>
+        <v>100594</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
